--- a/data/Lead_information_Formulario_Uruguay_Main.xlsx
+++ b/data/Lead_information_Formulario_Uruguay_Main.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,38 +481,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.uy/pickups/s10-lanzamiento-trail-boss</t>
+          <t>https://www.chevrolet.com.uy/autos/onix-plus-auto-familiar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/uruguay/gm_forms/S10-TRAILBOSS?model=s10</t>
+          <t>https://secure-developments.com/commonwealth/uruguay/gm_forms/movs-visid-quote?model=onix%20plus</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rafael Valentina</t>
+          <t>Diego</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Perez Rojas</t>
+          <t>Rodriguez</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69713514</t>
+          <t>68177637</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>096147801</t>
+          <t>093014736</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>rafaelvalentinaperezrojas_uy71@mrm.com</t>
+          <t>diegorodriguez_uy01@mrm.com</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -523,38 +523,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.uy/vehiculos-electricos/equinox-ev</t>
+          <t>https://www.chevrolet.com.uy/onstar/formulario-suscripcion-renovacion</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/uruguay/gm_forms/equinox-ev?model=equinox%20ev</t>
+          <t>https://secure-developments.com/commonwealth/uruguay/gm_forms/suscripcion-onstar?model=onstar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Alejandro</t>
+          <t>Sandra Agustina</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Diaz Salazar</t>
+          <t>Quispe</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16436143</t>
+          <t>12372222</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>098459020</t>
+          <t>091014577</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>alejandrodiazsalazar.uy30@mrm.com</t>
+          <t>sandraagustinaquispe_uy14@mrm.com</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -565,38 +565,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.uy/posventa/cambio-aceite-filtro</t>
+          <t>https://www.chevrolet.com.uy/solicita-una-cotizacion</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/uruguay/gm_forms/cambio-aceite-filtro?model=Posventa</t>
+          <t>https://secure-developments.com/commonwealth/uruguay/gm_forms/raq</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cristian</t>
+          <t>Gabriel Monica</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suarez Navarro</t>
+          <t>Navarro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45999981</t>
+          <t>48624121</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>096745354</t>
+          <t>091418879</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cristiansuareznavarro_uy39@mrm.com</t>
+          <t>gabrielmonicanavarro.uy62@mrm.com</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -604,48 +604,6 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.chevrolet.com.uy/solicita-una-cotizacion</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://secure-developments.com/commonwealth/uruguay/gm_forms/raq</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Rodrigo Javier</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Villanueva</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>67599793</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>092083121</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>rodrigojaviervillanueva_uy69@mrm.com</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Lead_information_Formulario_Uruguay_Main.xlsx
+++ b/data/Lead_information_Formulario_Uruguay_Main.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,38 +481,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.uy/autos/onix-plus-auto-familiar</t>
+          <t>https://www.chevrolet.com.uy/onstar/formulario-suscripcion-renovacion</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/uruguay/gm_forms/movs-visid-quote?model=onix%20plus</t>
+          <t>https://secure-developments.com/commonwealth/uruguay/gm_forms/suscripcion-onstar?model=onstar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Diego</t>
+          <t>Daniela Cristian</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rodriguez</t>
+          <t>Muñoz</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>68177637</t>
+          <t>76206625</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>093014736</t>
+          <t>098949535</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>diegorodriguez_uy01@mrm.com</t>
+          <t>danielacristianmunoz_uy42@mrm.com</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -523,38 +523,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.uy/onstar/formulario-suscripcion-renovacion</t>
+          <t>https://www.chevrolet.com.uy/pickups/silverado-camioneta-pickup</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/uruguay/gm_forms/suscripcion-onstar?model=onstar</t>
+          <t>https://secure-developments.com/commonwealth/uruguay/gm_forms/movs-visid-quote?model=silverado</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sandra Agustina</t>
+          <t>Marcelo Valentina</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Quispe</t>
+          <t>Silva Diaz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12372222</t>
+          <t>17556770</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>091014577</t>
+          <t>098338969</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>sandraagustinaquispe_uy14@mrm.com</t>
+          <t>marcelovalentinasilvadiaz.uy74@mrm.com</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -565,38 +565,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.uy/solicita-una-cotizacion</t>
+          <t>https://www.chevrolet.com.uy/vehiculos-electricos/spark-euv</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/uruguay/gm_forms/raq</t>
+          <t>https://secure-developments.com/commonwealth/uruguay/gm_forms/spark-euv?model=spark%20euv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Gabriel Monica</t>
+          <t>Sofia Agustina</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Navarro</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48624121</t>
+          <t>16211070</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>091418879</t>
+          <t>092720111</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>gabrielmonicanavarro.uy62@mrm.com</t>
+          <t>sofiaagustinabravo_uy21@mrm.com</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -604,6 +604,48 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.chevrolet.com.uy/solicita-una-cotizacion</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://secure-developments.com/commonwealth/uruguay/gm_forms/raq</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Verónica Patricia</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Navarro Vargas</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>41580278</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>095720468</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>veronicapatricianavarrovargas.uy86@mrm.com</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
